--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XI-XX/FRACC XIV/LTAIPT_A63F14.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XI-XX/FRACC XIV/LTAIPT_A63F14.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="495" windowWidth="19815" windowHeight="9405"/>
+    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -12,19 +12,21 @@
     <sheet name="Hidden_2" sheetId="3" r:id="rId3"/>
     <sheet name="Hidden_3" sheetId="4" r:id="rId4"/>
     <sheet name="Hidden_4" sheetId="5" r:id="rId5"/>
+    <sheet name="Hidden_5" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="Hidden_14">Hidden_1!$A$1:$A$4</definedName>
     <definedName name="Hidden_25">Hidden_2!$A$1:$A$2</definedName>
     <definedName name="Hidden_36">Hidden_3!$A$1:$A$3</definedName>
     <definedName name="Hidden_416">Hidden_4!$A$1:$A$5</definedName>
+    <definedName name="Hidden_523">Hidden_5!$A$1:$A$2</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="107">
   <si>
     <t>48961</t>
   </si>
@@ -122,6 +124,12 @@
     <t>435941</t>
   </si>
   <si>
+    <t>571922</t>
+  </si>
+  <si>
+    <t>571923</t>
+  </si>
+  <si>
     <t>435937</t>
   </si>
   <si>
@@ -131,6 +139,9 @@
     <t>435951</t>
   </si>
   <si>
+    <t>571924</t>
+  </si>
+  <si>
     <t>435945</t>
   </si>
   <si>
@@ -173,7 +184,7 @@
     <t xml:space="preserve">Clave o nivel del puesto </t>
   </si>
   <si>
-    <t>Denominación del puesto</t>
+    <t>Denominación del puesto (Redactados con perspectiva de género)</t>
   </si>
   <si>
     <t>Denominación del cargo o función</t>
@@ -194,13 +205,19 @@
     <t>Número de la convocatoria</t>
   </si>
   <si>
-    <t>Hipervínculo al documento</t>
+    <t>Hipervínculo al documento de la convocatoria, invitación y/o aviso (Redactados con perspectiva de género)</t>
   </si>
   <si>
     <t>Estado del proceso del concurso (catálogo)</t>
   </si>
   <si>
-    <t>Número total de candidatos registrados</t>
+    <t>Número total de candidato[a]s registrado[a]s</t>
+  </si>
+  <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; Total de candidatos hombres</t>
+  </si>
+  <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; Total de candidatas mujeres</t>
   </si>
   <si>
     <t>Nombre(s) de la persona aceptada</t>
@@ -212,7 +229,10 @@
     <t>Segundo apellido de la persona aceptada</t>
   </si>
   <si>
-    <t>Hipervínculo a la versión pública del acta</t>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; Sexo (catálogo)</t>
+  </si>
+  <si>
+    <t>Hipervínculo a la versión pública del acta o documento que al(la) ganador(a) (Redactadas con perspectiva de género)</t>
   </si>
   <si>
     <t>Hipervínculo al sistema electrónico de convocatorias y/o concursos, en su caso</t>
@@ -230,7 +250,7 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
+    <t>2023</t>
   </si>
   <si>
     <t>Concurso</t>
@@ -251,67 +271,82 @@
     <t>Docente frente a grupo</t>
   </si>
   <si>
-    <t>14/02/2022</t>
+    <t/>
+  </si>
+  <si>
+    <t>20/02/2023</t>
   </si>
   <si>
     <t>No aplica</t>
   </si>
   <si>
-    <t>http://public-file-system.usicamm.gob.mx/2022-2023/ad_media_superior/convocatoria/AEMS_COBACH_029.pdf</t>
+    <t>http://public-file-system.usicamm.gob.mx/2023-2024/AD/EMS/convocatoria/AEMS_COBACH_029.pdf</t>
+  </si>
+  <si>
+    <t>En proceso</t>
+  </si>
+  <si>
+    <t>USICAMM</t>
+  </si>
+  <si>
+    <t>01/04/2023</t>
+  </si>
+  <si>
+    <t>69EC679024E3ECBE22D026F1FA254B7A</t>
+  </si>
+  <si>
+    <t>30/06/2023</t>
+  </si>
+  <si>
+    <t>Convocatoria</t>
+  </si>
+  <si>
+    <t>Docente</t>
+  </si>
+  <si>
+    <t>347</t>
+  </si>
+  <si>
+    <t>148</t>
+  </si>
+  <si>
+    <t>199</t>
+  </si>
+  <si>
+    <t>01/07/2023</t>
+  </si>
+  <si>
+    <t>Invitación</t>
+  </si>
+  <si>
+    <t>Aviso</t>
+  </si>
+  <si>
+    <t>Abierto solo a servidores(as) públicos del Sujeto</t>
+  </si>
+  <si>
+    <t>Confianza</t>
+  </si>
+  <si>
+    <t>Base</t>
+  </si>
+  <si>
+    <t>En evaluación</t>
   </si>
   <si>
     <t>Finalizado</t>
   </si>
   <si>
-    <t>165</t>
-  </si>
-  <si>
-    <t>USICAMM</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>01/07/2022</t>
-  </si>
-  <si>
-    <t>93105F02B62D637A545D45018ACCBC66</t>
-  </si>
-  <si>
-    <t>01/04/2022</t>
-  </si>
-  <si>
-    <t>30/06/2022</t>
-  </si>
-  <si>
-    <t>Convocatoria</t>
-  </si>
-  <si>
-    <t>En evaluación</t>
-  </si>
-  <si>
-    <t>En proceso</t>
-  </si>
-  <si>
-    <t>Invitación</t>
-  </si>
-  <si>
-    <t>Aviso</t>
-  </si>
-  <si>
-    <t>Abierto solo a servidores(as) públicos del Sujeto</t>
-  </si>
-  <si>
-    <t>Confianza</t>
-  </si>
-  <si>
-    <t>Base</t>
-  </si>
-  <si>
     <t>Cancelado</t>
   </si>
   <si>
     <t>Desierto</t>
+  </si>
+  <si>
+    <t>Hombre</t>
+  </si>
+  <si>
+    <t>Mujer</t>
   </si>
 </sst>
 </file>
@@ -704,10 +739,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AA8"/>
+  <dimension ref="A1:AD8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.7109375" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36.140625" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -715,33 +750,35 @@
     <col min="6" max="6" width="27.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="29.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="42.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="56.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="29.42578125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="28.140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="58.7109375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="93.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="90.85546875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="37" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="34.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="30" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="33.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="35.5703125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="133.140625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="67" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="73.140625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="20" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="8" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="38.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="181.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="30" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="33.7109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="35.5703125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="181.85546875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="99.5703125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="84.28515625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="73.140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -758,7 +795,7 @@
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -773,7 +810,7 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -826,34 +863,43 @@
         <v>12</v>
       </c>
       <c r="S4" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T4" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="U4" t="s">
         <v>6</v>
       </c>
       <c r="V4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W4" t="s">
+        <v>6</v>
+      </c>
+      <c r="X4" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y4" t="s">
         <v>11</v>
       </c>
-      <c r="W4" t="s">
+      <c r="Z4" t="s">
         <v>11</v>
       </c>
-      <c r="X4" t="s">
+      <c r="AA4" t="s">
         <v>9</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="AB4" t="s">
         <v>7</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="AC4" t="s">
         <v>13</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AD4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>15</v>
       </c>
@@ -932,10 +978,19 @@
       <c r="AA5" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB5" t="s">
+        <v>41</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -963,120 +1018,132 @@
       <c r="Y6" s="4"/>
       <c r="Z6" s="4"/>
       <c r="AA6" s="4"/>
-    </row>
-    <row r="7" spans="1:27" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="AB6" s="4"/>
+      <c r="AC6" s="4"/>
+      <c r="AD6" s="4"/>
+    </row>
+    <row r="7" spans="1:30" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="AA7" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="AB7" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AC7" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AD7" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>81</v>
@@ -1085,25 +1152,25 @@
         <v>81</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="U8" s="2" t="s">
         <v>81</v>
@@ -1115,21 +1182,30 @@
         <v>81</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Z8" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AA8" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="AB8" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AC8" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD8" s="2" t="s">
         <v>81</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A6:AA6"/>
+    <mergeCell ref="A6:AD6"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
@@ -1137,18 +1213,21 @@
     <mergeCell ref="D3:F3"/>
     <mergeCell ref="G3:I3"/>
   </mergeCells>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E188">
+  <dataValidations count="5">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E200">
       <formula1>Hidden_14</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F8:F188">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F8:F200">
       <formula1>Hidden_25</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G8:G188">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G8:G200">
       <formula1>Hidden_36</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Q8:Q188">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Q8:Q200">
       <formula1>Hidden_416</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="X8:X200">
+      <formula1>Hidden_523</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1162,22 +1241,22 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -1192,12 +1271,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -1212,17 +1291,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -1237,27 +1316,47 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>78</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>95</v>
+        <v>104</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
